--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_16.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4475 +469,6330 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:22.075</t>
+          <t>2026-05-29 09:41:43.397</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779422004198</v>
+        <v>1780022501864</v>
       </c>
       <c r="C2" t="n">
-        <v>87403</v>
+        <v>82344</v>
       </c>
       <c r="D2" t="n">
-        <v>139.47</v>
+        <v>-88.28</v>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>806</v>
+        <v>1159</v>
       </c>
       <c r="G2" t="n">
-        <v>73.55</v>
+        <v>378.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1533</v>
+      </c>
+      <c r="L2" t="n">
+        <v>108</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.738</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:22.825</t>
+          <t>2026-05-29 09:41:43.398</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779422004400</v>
+        <v>1780022502064</v>
       </c>
       <c r="C3" t="n">
-        <v>87695</v>
+        <v>82087</v>
       </c>
       <c r="D3" t="n">
-        <v>424.49</v>
+        <v>-340.86</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>826</v>
+        <v>1159</v>
       </c>
       <c r="G3" t="n">
-        <v>75.01000000000001</v>
+        <v>378.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1334</v>
+      </c>
+      <c r="L3" t="n">
+        <v>107</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:22.826</t>
+          <t>2026-05-29 09:41:43.399</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779422004601</v>
+        <v>1780022502265</v>
       </c>
       <c r="C4" t="n">
-        <v>87452</v>
+        <v>81797</v>
       </c>
       <c r="D4" t="n">
-        <v>160.27</v>
+        <v>-613.8200000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F4" t="n">
-        <v>826</v>
+        <v>1159</v>
       </c>
       <c r="G4" t="n">
-        <v>75.01000000000001</v>
+        <v>378.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1134</v>
+      </c>
+      <c r="L4" t="n">
+        <v>105</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.539</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:22.831</t>
+          <t>2026-05-29 09:41:43.440</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779422004803</v>
+        <v>1780022502484</v>
       </c>
       <c r="C5" t="n">
-        <v>87347</v>
+        <v>81736</v>
       </c>
       <c r="D5" t="n">
-        <v>47.26</v>
+        <v>-644.13</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>826</v>
+        <v>1159</v>
       </c>
       <c r="G5" t="n">
-        <v>75.01000000000001</v>
+        <v>378.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K5" t="n">
+        <v>955</v>
+      </c>
+      <c r="L5" t="n">
+        <v>107</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:22.855</t>
+          <t>2026-05-29 09:41:44.222</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779422005004</v>
+        <v>1780022502684</v>
       </c>
       <c r="C6" t="n">
-        <v>87595</v>
+        <v>81629</v>
       </c>
       <c r="D6" t="n">
-        <v>292.89</v>
+        <v>-718.92</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>826</v>
+        <v>1159</v>
       </c>
       <c r="G6" t="n">
-        <v>75.01000000000001</v>
+        <v>378.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1537</v>
+      </c>
+      <c r="L6" t="n">
+        <v>112</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:23.252</t>
+          <t>2026-05-29 09:41:44.223</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779422005205</v>
+        <v>1780022502883</v>
       </c>
       <c r="C7" t="n">
-        <v>87928</v>
+        <v>81641</v>
       </c>
       <c r="D7" t="n">
-        <v>611.25</v>
+        <v>-670.97</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>705</v>
+        <v>1159</v>
       </c>
       <c r="G7" t="n">
-        <v>72.5</v>
+        <v>378.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1340</v>
+      </c>
+      <c r="L7" t="n">
+        <v>108</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.826</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:23.253</t>
+          <t>2026-05-29 09:41:44.230</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779422005407</v>
+        <v>1780022503084</v>
       </c>
       <c r="C8" t="n">
-        <v>87233</v>
+        <v>81632</v>
       </c>
       <c r="D8" t="n">
-        <v>-114.31</v>
+        <v>-646.4299999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>705</v>
+        <v>1159</v>
       </c>
       <c r="G8" t="n">
-        <v>72.5</v>
+        <v>378.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L8" t="n">
+        <v>105</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:23.872</t>
+          <t>2026-05-29 09:41:45.174</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779422005608</v>
+        <v>1780022503303</v>
       </c>
       <c r="C9" t="n">
-        <v>87432</v>
+        <v>81687</v>
       </c>
       <c r="D9" t="n">
-        <v>90.40000000000001</v>
+        <v>-559.1</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>705</v>
+        <v>1159</v>
       </c>
       <c r="G9" t="n">
-        <v>72.5</v>
+        <v>378.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="L9" t="n">
+        <v>119</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.904</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:23.873</t>
+          <t>2026-05-29 09:41:45.175</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779422005810</v>
+        <v>1780022503504</v>
       </c>
       <c r="C10" t="n">
-        <v>87569</v>
+        <v>82031</v>
       </c>
       <c r="D10" t="n">
-        <v>222.88</v>
+        <v>-187.15</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F10" t="n">
-        <v>705</v>
+        <v>2998</v>
       </c>
       <c r="G10" t="n">
-        <v>72.5</v>
+        <v>378.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L10" t="n">
+        <v>113</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:23.873</t>
+          <t>2026-05-29 09:41:45.176</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779422006011</v>
+        <v>1780022503703</v>
       </c>
       <c r="C11" t="n">
-        <v>87772</v>
+        <v>81605</v>
       </c>
       <c r="D11" t="n">
-        <v>414.74</v>
+        <v>-603.79</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>846</v>
+        <v>2998</v>
       </c>
       <c r="G11" t="n">
-        <v>75.18000000000001</v>
+        <v>378.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1472</v>
+      </c>
+      <c r="L11" t="n">
+        <v>119</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.633</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:24.356</t>
+          <t>2026-05-29 09:41:45.176</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779422006212</v>
+        <v>1780022503903</v>
       </c>
       <c r="C12" t="n">
-        <v>87353</v>
+        <v>82448</v>
       </c>
       <c r="D12" t="n">
-        <v>-25</v>
+        <v>269.4</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>846</v>
+        <v>2998</v>
       </c>
       <c r="G12" t="n">
-        <v>75.18000000000001</v>
+        <v>378.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1273</v>
+      </c>
+      <c r="L12" t="n">
+        <v>106</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.468</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:24.357</t>
+          <t>2026-05-29 09:41:45.713</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779422006414</v>
+        <v>1780022504122</v>
       </c>
       <c r="C13" t="n">
-        <v>87174</v>
+        <v>82406</v>
       </c>
       <c r="D13" t="n">
-        <v>-202.75</v>
+        <v>213.93</v>
       </c>
       <c r="E13" t="n">
         <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>846</v>
+        <v>640</v>
       </c>
       <c r="G13" t="n">
-        <v>75.18000000000001</v>
+        <v>353.95</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1590</v>
+      </c>
+      <c r="L13" t="n">
+        <v>102</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.906</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:24.678</t>
+          <t>2026-05-29 09:41:45.715</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779422006615</v>
+        <v>1780022504322</v>
       </c>
       <c r="C14" t="n">
-        <v>87399</v>
+        <v>82363</v>
       </c>
       <c r="D14" t="n">
-        <v>32.39</v>
+        <v>160.23</v>
       </c>
       <c r="E14" t="n">
         <v>75</v>
       </c>
       <c r="F14" t="n">
-        <v>846</v>
+        <v>640</v>
       </c>
       <c r="G14" t="n">
-        <v>75.18000000000001</v>
+        <v>353.95</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1391</v>
+      </c>
+      <c r="L14" t="n">
+        <v>107</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:24.679</t>
+          <t>2026-05-29 09:41:46.047</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779422006817</v>
+        <v>1780022504522</v>
       </c>
       <c r="C15" t="n">
-        <v>87750</v>
+        <v>81922</v>
       </c>
       <c r="D15" t="n">
-        <v>381.77</v>
+        <v>-288.78</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F15" t="n">
-        <v>845</v>
+        <v>640</v>
       </c>
       <c r="G15" t="n">
-        <v>74.37</v>
+        <v>353.95</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1524</v>
+      </c>
+      <c r="L15" t="n">
+        <v>106</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.054</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:25.220</t>
+          <t>2026-05-29 09:41:46.047</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779422007018</v>
+        <v>1780022504782</v>
       </c>
       <c r="C16" t="n">
-        <v>87957</v>
+        <v>82082</v>
       </c>
       <c r="D16" t="n">
-        <v>569.6799999999999</v>
+        <v>-114.34</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>845</v>
+        <v>640</v>
       </c>
       <c r="G16" t="n">
-        <v>74.37</v>
+        <v>353.95</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1265</v>
+      </c>
+      <c r="L16" t="n">
+        <v>108</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:25.221</t>
+          <t>2026-05-29 09:41:46.048</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779422007219</v>
+        <v>1780022504982</v>
       </c>
       <c r="C17" t="n">
-        <v>87130</v>
+        <v>82332</v>
       </c>
       <c r="D17" t="n">
-        <v>-285.8</v>
+        <v>141.38</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>845</v>
+        <v>640</v>
       </c>
       <c r="G17" t="n">
-        <v>74.37</v>
+        <v>353.95</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L17" t="n">
+        <v>111</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.508</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:25.560</t>
+          <t>2026-05-29 09:41:46.328</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779422007421</v>
+        <v>1780022505182</v>
       </c>
       <c r="C18" t="n">
-        <v>87382</v>
+        <v>82978</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.51</v>
+        <v>780.3099999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>845</v>
+        <v>1139</v>
       </c>
       <c r="G18" t="n">
-        <v>74.37</v>
+        <v>362.82</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1146</v>
+      </c>
+      <c r="L18" t="n">
+        <v>117</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.522</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:25.561</t>
+          <t>2026-05-29 09:41:46.394</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779422007622</v>
+        <v>1780022505382</v>
       </c>
       <c r="C19" t="n">
-        <v>87677</v>
+        <v>83069</v>
       </c>
       <c r="D19" t="n">
-        <v>276.46</v>
+        <v>832.29</v>
       </c>
       <c r="E19" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>845</v>
+        <v>1139</v>
       </c>
       <c r="G19" t="n">
-        <v>74.37</v>
+        <v>362.82</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1011</v>
+      </c>
+      <c r="L19" t="n">
+        <v>114</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.167</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:25.922</t>
+          <t>2026-05-29 09:41:46.680</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779422007824</v>
+        <v>1780022505582</v>
       </c>
       <c r="C20" t="n">
-        <v>88058</v>
+        <v>82853</v>
       </c>
       <c r="D20" t="n">
-        <v>643.64</v>
+        <v>574.6799999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F20" t="n">
-        <v>846</v>
+        <v>1139</v>
       </c>
       <c r="G20" t="n">
-        <v>71.41</v>
+        <v>362.82</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1098</v>
+      </c>
+      <c r="L20" t="n">
+        <v>116</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.702</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:25.923</t>
+          <t>2026-05-29 09:41:46.696</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779422008025</v>
+        <v>1780022505801</v>
       </c>
       <c r="C21" t="n">
-        <v>87271</v>
+        <v>83470</v>
       </c>
       <c r="D21" t="n">
-        <v>-175.54</v>
+        <v>1162.94</v>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>846</v>
+        <v>1139</v>
       </c>
       <c r="G21" t="n">
-        <v>71.41</v>
+        <v>362.82</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K21" t="n">
+        <v>894</v>
+      </c>
+      <c r="L21" t="n">
+        <v>120</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.242</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:26.441</t>
+          <t>2026-05-29 09:41:47.070</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779422008227</v>
+        <v>1780022506001</v>
       </c>
       <c r="C22" t="n">
-        <v>87607</v>
+        <v>83800</v>
       </c>
       <c r="D22" t="n">
-        <v>169.23</v>
+        <v>1434.8</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>846</v>
+        <v>1139</v>
       </c>
       <c r="G22" t="n">
-        <v>71.41</v>
+        <v>362.82</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L22" t="n">
+        <v>113</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.467</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:26.470</t>
+          <t>2026-05-29 09:41:47.270</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779422008428</v>
+        <v>1780022506201</v>
       </c>
       <c r="C23" t="n">
-        <v>87940</v>
+        <v>83991</v>
       </c>
       <c r="D23" t="n">
-        <v>493.77</v>
+        <v>1554.06</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>746</v>
+        <v>1139</v>
       </c>
       <c r="G23" t="n">
-        <v>53.98</v>
+        <v>362.82</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1067</v>
+      </c>
+      <c r="L23" t="n">
+        <v>115</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.187</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:26.471</t>
+          <t>2026-05-29 09:41:47.616</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779422008629</v>
+        <v>1780022506401</v>
       </c>
       <c r="C24" t="n">
-        <v>88219</v>
+        <v>84635</v>
       </c>
       <c r="D24" t="n">
-        <v>748.08</v>
+        <v>2120.35</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>746</v>
+        <v>1139</v>
       </c>
       <c r="G24" t="n">
-        <v>53.98</v>
+        <v>362.82</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1214</v>
+      </c>
+      <c r="L24" t="n">
+        <v>117</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.097</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:26.723</t>
+          <t>2026-05-29 09:41:47.617</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779422008831</v>
+        <v>1780022506601</v>
       </c>
       <c r="C25" t="n">
-        <v>87333</v>
+        <v>84200</v>
       </c>
       <c r="D25" t="n">
-        <v>-175.32</v>
+        <v>1579.34</v>
       </c>
       <c r="E25" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>746</v>
+        <v>1139</v>
       </c>
       <c r="G25" t="n">
-        <v>53.98</v>
+        <v>362.82</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1015</v>
+      </c>
+      <c r="L25" t="n">
+        <v>109</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.931</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:27.115</t>
+          <t>2026-05-29 09:41:47.978</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779422009032</v>
+        <v>1780022506801</v>
       </c>
       <c r="C26" t="n">
-        <v>87516</v>
+        <v>84285</v>
       </c>
       <c r="D26" t="n">
-        <v>16.45</v>
+        <v>1585.37</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>746</v>
+        <v>1139</v>
       </c>
       <c r="G26" t="n">
-        <v>53.98</v>
+        <v>362.82</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1176</v>
+      </c>
+      <c r="L26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.969</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:27.116</t>
+          <t>2026-05-29 09:41:47.979</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779422009234</v>
+        <v>1780022507001</v>
       </c>
       <c r="C27" t="n">
-        <v>87741</v>
+        <v>83634</v>
       </c>
       <c r="D27" t="n">
-        <v>240.62</v>
+        <v>855.1</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>746</v>
+        <v>1139</v>
       </c>
       <c r="G27" t="n">
-        <v>53.98</v>
+        <v>362.82</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>977</v>
+      </c>
+      <c r="L27" t="n">
+        <v>117</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.892</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:27.540</t>
+          <t>2026-05-29 09:41:48.313</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779422009435</v>
+        <v>1780022507220</v>
       </c>
       <c r="C28" t="n">
-        <v>87972</v>
+        <v>84520</v>
       </c>
       <c r="D28" t="n">
-        <v>459.59</v>
+        <v>1698.35</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>946</v>
+        <v>1139</v>
       </c>
       <c r="G28" t="n">
-        <v>71.09999999999999</v>
+        <v>362.82</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L28" t="n">
+        <v>117</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.649</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:27.541</t>
+          <t>2026-05-29 09:41:48.314</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779422009636</v>
+        <v>1780022507420</v>
       </c>
       <c r="C29" t="n">
-        <v>87085</v>
+        <v>84339</v>
       </c>
       <c r="D29" t="n">
-        <v>-450.39</v>
+        <v>1432.43</v>
       </c>
       <c r="E29" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>946</v>
+        <v>2178</v>
       </c>
       <c r="G29" t="n">
-        <v>71.09999999999999</v>
+        <v>362.82</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>893</v>
+      </c>
+      <c r="L29" t="n">
+        <v>112</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.031</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:28.149</t>
+          <t>2026-05-29 09:41:49.266</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779422009838</v>
+        <v>1780022507620</v>
       </c>
       <c r="C30" t="n">
-        <v>87283</v>
+        <v>85149</v>
       </c>
       <c r="D30" t="n">
-        <v>-229.87</v>
+        <v>2170.81</v>
       </c>
       <c r="E30" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F30" t="n">
-        <v>946</v>
+        <v>2178</v>
       </c>
       <c r="G30" t="n">
-        <v>71.09999999999999</v>
+        <v>362.82</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1645</v>
+      </c>
+      <c r="L30" t="n">
+        <v>118</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:28.149</t>
+          <t>2026-05-29 09:41:49.282</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779422010039</v>
+        <v>1780022507820</v>
       </c>
       <c r="C31" t="n">
-        <v>87489</v>
+        <v>84905</v>
       </c>
       <c r="D31" t="n">
-        <v>-12.37</v>
+        <v>1818.27</v>
       </c>
       <c r="E31" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>946</v>
+        <v>2178</v>
       </c>
       <c r="G31" t="n">
-        <v>71.09999999999999</v>
+        <v>362.82</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1461</v>
+      </c>
+      <c r="L31" t="n">
+        <v>123</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.428</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:28.450</t>
+          <t>2026-05-29 09:41:49.711</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779422010241</v>
+        <v>1780022508020</v>
       </c>
       <c r="C32" t="n">
-        <v>87688</v>
+        <v>84481</v>
       </c>
       <c r="D32" t="n">
-        <v>187.24</v>
+        <v>1303.35</v>
       </c>
       <c r="E32" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F32" t="n">
-        <v>826</v>
+        <v>2178</v>
       </c>
       <c r="G32" t="n">
-        <v>64.97</v>
+        <v>362.82</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1689</v>
+      </c>
+      <c r="L32" t="n">
+        <v>106</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.738</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:28.451</t>
+          <t>2026-05-29 09:41:49.714</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779422010442</v>
+        <v>1780022508220</v>
       </c>
       <c r="C33" t="n">
-        <v>86825</v>
+        <v>84225</v>
       </c>
       <c r="D33" t="n">
-        <v>-685.12</v>
+        <v>982.1900000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F33" t="n">
-        <v>826</v>
+        <v>2178</v>
       </c>
       <c r="G33" t="n">
-        <v>64.97</v>
+        <v>362.82</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1492</v>
+      </c>
+      <c r="L33" t="n">
+        <v>121</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.551</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:28.451</t>
+          <t>2026-05-29 09:41:49.724</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779422010644</v>
+        <v>1780022508420</v>
       </c>
       <c r="C34" t="n">
-        <v>86977</v>
+        <v>84302</v>
       </c>
       <c r="D34" t="n">
-        <v>-498.86</v>
+        <v>1010.08</v>
       </c>
       <c r="E34" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F34" t="n">
-        <v>826</v>
+        <v>2178</v>
       </c>
       <c r="G34" t="n">
-        <v>64.97</v>
+        <v>362.82</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1303</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.157</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:28.752</t>
+          <t>2026-05-29 09:41:49.753</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779422010845</v>
+        <v>1780022508620</v>
       </c>
       <c r="C35" t="n">
-        <v>87151</v>
+        <v>84117</v>
       </c>
       <c r="D35" t="n">
-        <v>-299.92</v>
+        <v>774.5700000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F35" t="n">
-        <v>826</v>
+        <v>2178</v>
       </c>
       <c r="G35" t="n">
-        <v>64.97</v>
+        <v>362.82</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1132</v>
+      </c>
+      <c r="L35" t="n">
+        <v>108</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.014</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:29.186</t>
+          <t>2026-05-29 09:41:49.957</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779422011046</v>
+        <v>1780022508839</v>
       </c>
       <c r="C36" t="n">
-        <v>87395</v>
+        <v>83930</v>
       </c>
       <c r="D36" t="n">
-        <v>-40.92</v>
+        <v>548.84</v>
       </c>
       <c r="E36" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F36" t="n">
-        <v>886</v>
+        <v>2178</v>
       </c>
       <c r="G36" t="n">
-        <v>67.14</v>
+        <v>362.82</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1116</v>
+      </c>
+      <c r="L36" t="n">
+        <v>111</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.668</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:29.187</t>
+          <t>2026-05-29 09:41:49.958</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779422011248</v>
+        <v>1780022509039</v>
       </c>
       <c r="C37" t="n">
-        <v>87372</v>
+        <v>83934</v>
       </c>
       <c r="D37" t="n">
-        <v>-61.88</v>
+        <v>525.4</v>
       </c>
       <c r="E37" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F37" t="n">
-        <v>886</v>
+        <v>2178</v>
       </c>
       <c r="G37" t="n">
-        <v>67.14</v>
+        <v>362.82</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J37" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K37" t="n">
+        <v>918</v>
+      </c>
+      <c r="L37" t="n">
+        <v>117</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.861</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:29.187</t>
+          <t>2026-05-29 09:41:50.715</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779422011449</v>
+        <v>1780022509240</v>
       </c>
       <c r="C38" t="n">
-        <v>86697</v>
+        <v>84137</v>
       </c>
       <c r="D38" t="n">
-        <v>-733.78</v>
+        <v>702.13</v>
       </c>
       <c r="E38" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F38" t="n">
-        <v>886</v>
+        <v>2178</v>
       </c>
       <c r="G38" t="n">
-        <v>67.14</v>
+        <v>362.82</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1474</v>
+      </c>
+      <c r="L38" t="n">
+        <v>108</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.792</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:29.577</t>
+          <t>2026-05-29 09:41:50.715</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779422011651</v>
+        <v>1780022509439</v>
       </c>
       <c r="C39" t="n">
-        <v>86869</v>
+        <v>83972</v>
       </c>
       <c r="D39" t="n">
-        <v>-525.09</v>
+        <v>502.02</v>
       </c>
       <c r="E39" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>886</v>
+        <v>2178</v>
       </c>
       <c r="G39" t="n">
-        <v>67.14</v>
+        <v>362.82</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1276</v>
+      </c>
+      <c r="L39" t="n">
+        <v>115</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:29.603</t>
+          <t>2026-05-29 09:41:51.244</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779422011852</v>
+        <v>1780022509640</v>
       </c>
       <c r="C40" t="n">
-        <v>87081</v>
+        <v>83995</v>
       </c>
       <c r="D40" t="n">
-        <v>-286.84</v>
+        <v>499.92</v>
       </c>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>886</v>
+        <v>2178</v>
       </c>
       <c r="G40" t="n">
-        <v>67.14</v>
+        <v>362.82</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1603</v>
+      </c>
+      <c r="L40" t="n">
+        <v>148</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.696</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:29.994</t>
+          <t>2026-05-29 09:41:51.245</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779422012053</v>
+        <v>1780022509839</v>
       </c>
       <c r="C41" t="n">
-        <v>87228</v>
+        <v>83702</v>
       </c>
       <c r="D41" t="n">
-        <v>-125.5</v>
+        <v>181.93</v>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
-        <v>887</v>
+        <v>2178</v>
       </c>
       <c r="G41" t="n">
-        <v>69.08</v>
+        <v>362.82</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L41" t="n">
+        <v>129</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:29.995</t>
+          <t>2026-05-29 09:41:51.246</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779422012255</v>
+        <v>1780022510039</v>
       </c>
       <c r="C42" t="n">
-        <v>86501</v>
+        <v>83893</v>
       </c>
       <c r="D42" t="n">
-        <v>-846.22</v>
+        <v>363.83</v>
       </c>
       <c r="E42" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F42" t="n">
-        <v>887</v>
+        <v>2178</v>
       </c>
       <c r="G42" t="n">
-        <v>69.08</v>
+        <v>362.82</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L42" t="n">
+        <v>96</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.076</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:30.398</t>
+          <t>2026-05-29 09:41:51.247</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779422012456</v>
+        <v>1780022510239</v>
       </c>
       <c r="C43" t="n">
-        <v>86754</v>
+        <v>84050</v>
       </c>
       <c r="D43" t="n">
-        <v>-550.91</v>
+        <v>502.64</v>
       </c>
       <c r="E43" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F43" t="n">
-        <v>887</v>
+        <v>2178</v>
       </c>
       <c r="G43" t="n">
-        <v>69.08</v>
+        <v>362.82</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L43" t="n">
+        <v>116</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:30.398</t>
+          <t>2026-05-29 09:41:52.317</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779422012658</v>
+        <v>1780022510458</v>
       </c>
       <c r="C44" t="n">
-        <v>87075</v>
+        <v>84037</v>
       </c>
       <c r="D44" t="n">
-        <v>-202.37</v>
+        <v>464.51</v>
       </c>
       <c r="E44" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F44" t="n">
-        <v>887</v>
+        <v>2978</v>
       </c>
       <c r="G44" t="n">
-        <v>69.08</v>
+        <v>362.82</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1858</v>
+      </c>
+      <c r="L44" t="n">
+        <v>126</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.767</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:30.816</t>
+          <t>2026-05-29 09:41:52.318</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779422012859</v>
+        <v>1780022510658</v>
       </c>
       <c r="C45" t="n">
-        <v>87398</v>
+        <v>84224</v>
       </c>
       <c r="D45" t="n">
-        <v>130.75</v>
+        <v>628.28</v>
       </c>
       <c r="E45" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F45" t="n">
-        <v>745</v>
+        <v>2978</v>
       </c>
       <c r="G45" t="n">
-        <v>74.87</v>
+        <v>362.82</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1659</v>
+      </c>
+      <c r="L45" t="n">
+        <v>110</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.829</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:30.817</t>
+          <t>2026-05-29 09:41:52.697</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779422013060</v>
+        <v>1780022510858</v>
       </c>
       <c r="C46" t="n">
-        <v>86567</v>
+        <v>84130</v>
       </c>
       <c r="D46" t="n">
-        <v>-706.79</v>
+        <v>502.87</v>
       </c>
       <c r="E46" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>745</v>
+        <v>2978</v>
       </c>
       <c r="G46" t="n">
-        <v>74.87</v>
+        <v>362.82</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1838</v>
+      </c>
+      <c r="L46" t="n">
+        <v>122</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:31.213</t>
+          <t>2026-05-29 09:41:52.699</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779422013262</v>
+        <v>1780022511058</v>
       </c>
       <c r="C47" t="n">
-        <v>86824</v>
+        <v>84363</v>
       </c>
       <c r="D47" t="n">
-        <v>-414.45</v>
+        <v>710.72</v>
       </c>
       <c r="E47" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F47" t="n">
-        <v>745</v>
+        <v>2978</v>
       </c>
       <c r="G47" t="n">
-        <v>74.87</v>
+        <v>362.82</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1640</v>
+      </c>
+      <c r="L47" t="n">
+        <v>105</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.126</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:31.213</t>
+          <t>2026-05-29 09:41:52.700</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779422013463</v>
+        <v>1780022511258</v>
       </c>
       <c r="C48" t="n">
-        <v>87091</v>
+        <v>84044</v>
       </c>
       <c r="D48" t="n">
-        <v>-126.72</v>
+        <v>356.19</v>
       </c>
       <c r="E48" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F48" t="n">
-        <v>745</v>
+        <v>2978</v>
       </c>
       <c r="G48" t="n">
-        <v>74.87</v>
+        <v>362.82</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1441</v>
+      </c>
+      <c r="L48" t="n">
+        <v>109</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.653</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:31.621</t>
+          <t>2026-05-29 09:41:52.701</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779422013665</v>
+        <v>1780022511458</v>
       </c>
       <c r="C49" t="n">
-        <v>87323</v>
+        <v>83550</v>
       </c>
       <c r="D49" t="n">
-        <v>111.61</v>
+        <v>-155.62</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F49" t="n">
-        <v>805</v>
+        <v>2978</v>
       </c>
       <c r="G49" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1242</v>
+      </c>
+      <c r="L49" t="n">
+        <v>108</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:31.622</t>
+          <t>2026-05-29 09:41:52.940</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779422013866</v>
+        <v>1780022511658</v>
       </c>
       <c r="C50" t="n">
-        <v>86469</v>
+        <v>84750</v>
       </c>
       <c r="D50" t="n">
-        <v>-747.97</v>
+        <v>1052.16</v>
       </c>
       <c r="E50" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F50" t="n">
-        <v>805</v>
+        <v>2978</v>
       </c>
       <c r="G50" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1281</v>
+      </c>
+      <c r="L50" t="n">
+        <v>113</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:32.136</t>
+          <t>2026-05-29 09:41:52.954</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779422014067</v>
+        <v>1780022511877</v>
       </c>
       <c r="C51" t="n">
-        <v>86740</v>
+        <v>84956</v>
       </c>
       <c r="D51" t="n">
-        <v>-439.57</v>
+        <v>1205.55</v>
       </c>
       <c r="E51" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F51" t="n">
-        <v>805</v>
+        <v>1500</v>
       </c>
       <c r="G51" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J51" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1076</v>
+      </c>
+      <c r="L51" t="n">
+        <v>116</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.716</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:32.150</t>
+          <t>2026-05-29 09:41:52.956</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779422014269</v>
+        <v>1780022512077</v>
       </c>
       <c r="C52" t="n">
-        <v>86999</v>
+        <v>84918</v>
       </c>
       <c r="D52" t="n">
-        <v>-158.59</v>
+        <v>1107.27</v>
       </c>
       <c r="E52" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F52" t="n">
-        <v>805</v>
+        <v>1500</v>
       </c>
       <c r="G52" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>878</v>
+      </c>
+      <c r="L52" t="n">
+        <v>119</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.865</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:32.468</t>
+          <t>2026-05-29 09:41:54.254</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779422014470</v>
+        <v>1780022512277</v>
       </c>
       <c r="C53" t="n">
-        <v>87238</v>
+        <v>82359</v>
       </c>
       <c r="D53" t="n">
-        <v>88.34</v>
+        <v>-1507.09</v>
       </c>
       <c r="E53" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>846</v>
+        <v>1500</v>
       </c>
       <c r="G53" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1976</v>
+      </c>
+      <c r="L53" t="n">
+        <v>117</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.854</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:32.468</t>
+          <t>2026-05-29 09:41:54.255</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779422014672</v>
+        <v>1780022512477</v>
       </c>
       <c r="C54" t="n">
-        <v>86388</v>
+        <v>81942</v>
       </c>
       <c r="D54" t="n">
-        <v>-766.08</v>
+        <v>-1848.73</v>
       </c>
       <c r="E54" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>846</v>
+        <v>1500</v>
       </c>
       <c r="G54" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1778</v>
+      </c>
+      <c r="L54" t="n">
+        <v>112</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.846</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:32.860</t>
+          <t>2026-05-29 09:41:54.262</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779422014873</v>
+        <v>1780022512677</v>
       </c>
       <c r="C55" t="n">
-        <v>86636</v>
+        <v>82064</v>
       </c>
       <c r="D55" t="n">
-        <v>-479.77</v>
+        <v>-1634.3</v>
       </c>
       <c r="E55" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>846</v>
+        <v>1500</v>
       </c>
       <c r="G55" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1584</v>
+      </c>
+      <c r="L55" t="n">
+        <v>115</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:32.861</t>
+          <t>2026-05-29 09:41:54.263</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779422015074</v>
+        <v>1780022512877</v>
       </c>
       <c r="C56" t="n">
-        <v>86881</v>
+        <v>82349</v>
       </c>
       <c r="D56" t="n">
-        <v>-210.79</v>
+        <v>-1267.58</v>
       </c>
       <c r="E56" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>846</v>
+        <v>1500</v>
       </c>
       <c r="G56" t="n">
-        <v>62.26</v>
+        <v>362.82</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1385</v>
+      </c>
+      <c r="L56" t="n">
+        <v>111</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.837</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:33.288</t>
+          <t>2026-05-29 09:41:54.265</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779422015276</v>
+        <v>1780022513077</v>
       </c>
       <c r="C57" t="n">
-        <v>87120</v>
+        <v>83133</v>
       </c>
       <c r="D57" t="n">
-        <v>38.75</v>
+        <v>-420.2</v>
       </c>
       <c r="E57" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F57" t="n">
-        <v>866</v>
+        <v>1500</v>
       </c>
       <c r="G57" t="n">
-        <v>62.89</v>
+        <v>362.82</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1187</v>
+      </c>
+      <c r="L57" t="n">
+        <v>107</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.212</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:33.288</t>
+          <t>2026-05-29 09:41:54.266</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779422015477</v>
+        <v>1780022513277</v>
       </c>
       <c r="C58" t="n">
-        <v>86286</v>
+        <v>82886</v>
       </c>
       <c r="D58" t="n">
-        <v>-797.1799999999999</v>
+        <v>-646.1900000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F58" t="n">
-        <v>866</v>
+        <v>1500</v>
       </c>
       <c r="G58" t="n">
-        <v>62.89</v>
+        <v>362.82</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>988</v>
+      </c>
+      <c r="L58" t="n">
+        <v>116</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:33.683</t>
+          <t>2026-05-29 09:41:55.546</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779422015679</v>
+        <v>1780022513496</v>
       </c>
       <c r="C59" t="n">
-        <v>86458</v>
+        <v>81998</v>
       </c>
       <c r="D59" t="n">
-        <v>-585.33</v>
+        <v>-1501.88</v>
       </c>
       <c r="E59" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F59" t="n">
-        <v>866</v>
+        <v>1500</v>
       </c>
       <c r="G59" t="n">
-        <v>62.89</v>
+        <v>362.82</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2049</v>
+      </c>
+      <c r="L59" t="n">
+        <v>107</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.555</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:33.684</t>
+          <t>2026-05-29 09:41:55.548</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779422015880</v>
+        <v>1780022513696</v>
       </c>
       <c r="C60" t="n">
-        <v>86635</v>
+        <v>83452</v>
       </c>
       <c r="D60" t="n">
-        <v>-379.06</v>
+        <v>27.21</v>
       </c>
       <c r="E60" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F60" t="n">
-        <v>866</v>
+        <v>1500</v>
       </c>
       <c r="G60" t="n">
-        <v>62.89</v>
+        <v>362.82</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1850</v>
+      </c>
+      <c r="L60" t="n">
+        <v>119</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.434</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:34.081</t>
+          <t>2026-05-29 09:41:55.549</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779422016081</v>
+        <v>1780022513896</v>
       </c>
       <c r="C61" t="n">
-        <v>86792</v>
+        <v>82280</v>
       </c>
       <c r="D61" t="n">
-        <v>-203.11</v>
+        <v>-1146.15</v>
       </c>
       <c r="E61" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>866</v>
+        <v>1500</v>
       </c>
       <c r="G61" t="n">
-        <v>63.42</v>
+        <v>362.82</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1652</v>
+      </c>
+      <c r="L61" t="n">
+        <v>115</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.123</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:34.082</t>
+          <t>2026-05-29 09:41:55.615</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779422016283</v>
+        <v>1780022514096</v>
       </c>
       <c r="C62" t="n">
-        <v>85942</v>
+        <v>82694</v>
       </c>
       <c r="D62" t="n">
-        <v>-1042.95</v>
+        <v>-674.84</v>
       </c>
       <c r="E62" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>866</v>
+        <v>1500</v>
       </c>
       <c r="G62" t="n">
-        <v>63.42</v>
+        <v>362.82</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1518</v>
+      </c>
+      <c r="L62" t="n">
+        <v>119</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:34.488</t>
+          <t>2026-05-29 09:41:55.616</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779422016484</v>
+        <v>1780022514296</v>
       </c>
       <c r="C63" t="n">
-        <v>86278</v>
+        <v>82773</v>
       </c>
       <c r="D63" t="n">
-        <v>-654.8</v>
+        <v>-562.1</v>
       </c>
       <c r="E63" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>866</v>
+        <v>1500</v>
       </c>
       <c r="G63" t="n">
-        <v>63.42</v>
+        <v>362.82</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1319</v>
+      </c>
+      <c r="L63" t="n">
+        <v>106</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.148</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:34.488</t>
+          <t>2026-05-29 09:41:55.618</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779422016686</v>
+        <v>1780022514496</v>
       </c>
       <c r="C64" t="n">
-        <v>86529</v>
+        <v>82412</v>
       </c>
       <c r="D64" t="n">
-        <v>-371.06</v>
+        <v>-895</v>
       </c>
       <c r="E64" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>866</v>
+        <v>2538</v>
       </c>
       <c r="G64" t="n">
-        <v>63.42</v>
+        <v>362.82</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1120</v>
+      </c>
+      <c r="L64" t="n">
+        <v>109</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.146</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:34.919</t>
+          <t>2026-05-29 09:41:55.619</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779422016887</v>
+        <v>1780022514696</v>
       </c>
       <c r="C65" t="n">
-        <v>86771</v>
+        <v>82662</v>
       </c>
       <c r="D65" t="n">
-        <v>-110.51</v>
+        <v>-600.25</v>
       </c>
       <c r="E65" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F65" t="n">
-        <v>746</v>
+        <v>2538</v>
       </c>
       <c r="G65" t="n">
-        <v>63.42</v>
+        <v>362.82</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>922</v>
+      </c>
+      <c r="L65" t="n">
+        <v>113</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.007</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:34.920</t>
+          <t>2026-05-29 09:41:56.031</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779422017089</v>
+        <v>1780022514896</v>
       </c>
       <c r="C66" t="n">
-        <v>86053</v>
+        <v>82913</v>
       </c>
       <c r="D66" t="n">
-        <v>-822.98</v>
+        <v>-319.23</v>
       </c>
       <c r="E66" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F66" t="n">
-        <v>746</v>
+        <v>560</v>
       </c>
       <c r="G66" t="n">
-        <v>63.42</v>
+        <v>360.63</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1134</v>
+      </c>
+      <c r="L66" t="n">
+        <v>105</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.911</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:35.389</t>
+          <t>2026-05-29 09:41:56.056</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779422017290</v>
+        <v>1780022515115</v>
       </c>
       <c r="C67" t="n">
-        <v>86301</v>
+        <v>82916</v>
       </c>
       <c r="D67" t="n">
-        <v>-533.84</v>
+        <v>-300.27</v>
       </c>
       <c r="E67" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F67" t="n">
-        <v>746</v>
+        <v>560</v>
       </c>
       <c r="G67" t="n">
-        <v>63.42</v>
+        <v>360.63</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>940</v>
+      </c>
+      <c r="L67" t="n">
+        <v>115</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.013</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:35.390</t>
+          <t>2026-05-29 09:41:56.512</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779422017491</v>
+        <v>1780022515315</v>
       </c>
       <c r="C68" t="n">
-        <v>86628</v>
+        <v>82793</v>
       </c>
       <c r="D68" t="n">
-        <v>-180.14</v>
+        <v>-408.26</v>
       </c>
       <c r="E68" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F68" t="n">
-        <v>746</v>
+        <v>560</v>
       </c>
       <c r="G68" t="n">
-        <v>63.42</v>
+        <v>360.63</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1197</v>
+      </c>
+      <c r="L68" t="n">
+        <v>107</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.574</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:35.725</t>
+          <t>2026-05-29 09:41:56.513</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779422017693</v>
+        <v>1780022515515</v>
       </c>
       <c r="C69" t="n">
-        <v>86886</v>
+        <v>83054</v>
       </c>
       <c r="D69" t="n">
-        <v>86.86</v>
+        <v>-126.85</v>
       </c>
       <c r="E69" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F69" t="n">
-        <v>745</v>
+        <v>560</v>
       </c>
       <c r="G69" t="n">
-        <v>58.41</v>
+        <v>360.63</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>998</v>
+      </c>
+      <c r="L69" t="n">
+        <v>104</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.537</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:35.725</t>
+          <t>2026-05-29 09:41:57.319</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779422017894</v>
+        <v>1780022515715</v>
       </c>
       <c r="C70" t="n">
-        <v>86667</v>
+        <v>82808</v>
       </c>
       <c r="D70" t="n">
-        <v>-136.48</v>
+        <v>-366.5</v>
       </c>
       <c r="E70" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F70" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G70" t="n">
-        <v>58.41</v>
+        <v>365.44</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1603</v>
+      </c>
+      <c r="L70" t="n">
+        <v>107</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.126</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:36.158</t>
+          <t>2026-05-29 09:41:57.322</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779422018096</v>
+        <v>1780022515915</v>
       </c>
       <c r="C71" t="n">
-        <v>86255</v>
+        <v>83079</v>
       </c>
       <c r="D71" t="n">
-        <v>-541.66</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F71" t="n">
-        <v>745</v>
+        <v>719</v>
       </c>
       <c r="G71" t="n">
-        <v>58.41</v>
+        <v>365.44</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1405</v>
+      </c>
+      <c r="L71" t="n">
+        <v>108</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.437</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:36.158</t>
+          <t>2026-05-29 09:41:57.323</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779422018297</v>
+        <v>1780022516115</v>
       </c>
       <c r="C72" t="n">
-        <v>86464</v>
+        <v>83387</v>
       </c>
       <c r="D72" t="n">
-        <v>-305.57</v>
+        <v>234.68</v>
       </c>
       <c r="E72" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F72" t="n">
-        <v>745</v>
+        <v>420</v>
       </c>
       <c r="G72" t="n">
-        <v>58.41</v>
+        <v>367</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1207</v>
+      </c>
+      <c r="L72" t="n">
+        <v>104</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.255</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:37.521</t>
+          <t>2026-05-29 09:41:58.207</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779422018498</v>
+        <v>1780022516315</v>
       </c>
       <c r="C73" t="n">
-        <v>86726</v>
+        <v>83660</v>
       </c>
       <c r="D73" t="n">
-        <v>-28.29</v>
+        <v>495.95</v>
       </c>
       <c r="E73" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F73" t="n">
-        <v>946</v>
+        <v>420</v>
       </c>
       <c r="G73" t="n">
-        <v>70.45999999999999</v>
+        <v>367</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1891</v>
+      </c>
+      <c r="L73" t="n">
+        <v>109</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.961</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:37.522</t>
+          <t>2026-05-29 09:41:58.213</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779422018700</v>
+        <v>1780022516534</v>
       </c>
       <c r="C74" t="n">
-        <v>86563</v>
+        <v>83748</v>
       </c>
       <c r="D74" t="n">
-        <v>-189.88</v>
+        <v>559.15</v>
       </c>
       <c r="E74" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F74" t="n">
-        <v>946</v>
+        <v>420</v>
       </c>
       <c r="G74" t="n">
-        <v>70.45999999999999</v>
+        <v>367</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1678</v>
+      </c>
+      <c r="L74" t="n">
+        <v>107</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.012</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:37.523</t>
+          <t>2026-05-29 09:41:58.214</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779422018901</v>
+        <v>1780022516734</v>
       </c>
       <c r="C75" t="n">
-        <v>86161</v>
+        <v>83573</v>
       </c>
       <c r="D75" t="n">
-        <v>-582.39</v>
+        <v>356.19</v>
       </c>
       <c r="E75" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F75" t="n">
-        <v>946</v>
+        <v>420</v>
       </c>
       <c r="G75" t="n">
-        <v>70.45999999999999</v>
+        <v>367</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1479</v>
+      </c>
+      <c r="L75" t="n">
+        <v>106</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.926</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:37.523</t>
+          <t>2026-05-29 09:41:58.215</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779422019103</v>
+        <v>1780022516934</v>
       </c>
       <c r="C76" t="n">
-        <v>86411</v>
+        <v>83731</v>
       </c>
       <c r="D76" t="n">
-        <v>-303.27</v>
+        <v>496.38</v>
       </c>
       <c r="E76" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F76" t="n">
-        <v>946</v>
+        <v>420</v>
       </c>
       <c r="G76" t="n">
-        <v>70.45999999999999</v>
+        <v>367</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L76" t="n">
+        <v>106</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:37.558</t>
+          <t>2026-05-29 09:41:58.751</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779422019304</v>
+        <v>1780022517134</v>
       </c>
       <c r="C77" t="n">
-        <v>86710</v>
+        <v>83900</v>
       </c>
       <c r="D77" t="n">
-        <v>10.9</v>
+        <v>640.5599999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F77" t="n">
-        <v>786</v>
+        <v>420</v>
       </c>
       <c r="G77" t="n">
-        <v>69.31</v>
+        <v>367</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1616</v>
+      </c>
+      <c r="L77" t="n">
+        <v>106</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.654</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:37.558</t>
+          <t>2026-05-29 09:41:58.752</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779422019505</v>
+        <v>1780022517334</v>
       </c>
       <c r="C78" t="n">
-        <v>86691</v>
+        <v>83565</v>
       </c>
       <c r="D78" t="n">
-        <v>-8.65</v>
+        <v>273.54</v>
       </c>
       <c r="E78" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F78" t="n">
-        <v>786</v>
+        <v>420</v>
       </c>
       <c r="G78" t="n">
-        <v>69.31</v>
+        <v>367</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J78" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1417</v>
+      </c>
+      <c r="L78" t="n">
+        <v>113</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.616</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.175</t>
+          <t>2026-05-29 09:41:59.477</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779422019707</v>
+        <v>1780022517534</v>
       </c>
       <c r="C79" t="n">
-        <v>86136</v>
+        <v>82696</v>
       </c>
       <c r="D79" t="n">
-        <v>-563.22</v>
+        <v>-609.14</v>
       </c>
       <c r="E79" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F79" t="n">
-        <v>786</v>
+        <v>420</v>
       </c>
       <c r="G79" t="n">
-        <v>69.31</v>
+        <v>367</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J79" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1942</v>
+      </c>
+      <c r="L79" t="n">
+        <v>107</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.176</t>
+          <t>2026-05-29 09:41:59.481</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779422019908</v>
+        <v>1780022517854</v>
       </c>
       <c r="C80" t="n">
-        <v>86435</v>
+        <v>82495</v>
       </c>
       <c r="D80" t="n">
-        <v>-236.05</v>
+        <v>-779.6799999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="F80" t="n">
-        <v>786</v>
+        <v>420</v>
       </c>
       <c r="G80" t="n">
-        <v>69.31</v>
+        <v>367</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1626</v>
+      </c>
+      <c r="L80" t="n">
+        <v>108</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.666</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.176</t>
+          <t>2026-05-29 09:41:59.482</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779422020110</v>
+        <v>1780022518073</v>
       </c>
       <c r="C81" t="n">
-        <v>86731</v>
+        <v>81755</v>
       </c>
       <c r="D81" t="n">
-        <v>71.75</v>
+        <v>-1480.7</v>
       </c>
       <c r="E81" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F81" t="n">
-        <v>805</v>
+        <v>420</v>
       </c>
       <c r="G81" t="n">
-        <v>65.76000000000001</v>
+        <v>367</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1408</v>
+      </c>
+      <c r="L81" t="n">
+        <v>117</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.664</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.177</t>
+          <t>2026-05-29 09:41:59.638</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779422020311</v>
+        <v>1780022518273</v>
       </c>
       <c r="C82" t="n">
-        <v>87009</v>
+        <v>82978</v>
       </c>
       <c r="D82" t="n">
-        <v>346.16</v>
+        <v>-183.67</v>
       </c>
       <c r="E82" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F82" t="n">
-        <v>805</v>
+        <v>420</v>
       </c>
       <c r="G82" t="n">
-        <v>65.76000000000001</v>
+        <v>367</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L82" t="n">
+        <v>114</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.635</t>
+          <t>2026-05-29 09:41:59.639</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779422020512</v>
+        <v>1780022518473</v>
       </c>
       <c r="C83" t="n">
-        <v>86125</v>
+        <v>82762</v>
       </c>
       <c r="D83" t="n">
-        <v>-555.15</v>
+        <v>-390.48</v>
       </c>
       <c r="E83" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F83" t="n">
-        <v>805</v>
+        <v>420</v>
       </c>
       <c r="G83" t="n">
-        <v>65.76000000000001</v>
+        <v>367</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L83" t="n">
+        <v>117</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.914</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.636</t>
+          <t>2026-05-29 09:41:59.640</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779422020714</v>
+        <v>1780022518673</v>
       </c>
       <c r="C84" t="n">
-        <v>86391</v>
+        <v>83118</v>
       </c>
       <c r="D84" t="n">
-        <v>-261.39</v>
+        <v>-14.96</v>
       </c>
       <c r="E84" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F84" t="n">
-        <v>805</v>
+        <v>420</v>
       </c>
       <c r="G84" t="n">
-        <v>65.76000000000001</v>
+        <v>367</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K84" t="n">
+        <v>966</v>
+      </c>
+      <c r="L84" t="n">
+        <v>104</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.902</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.995</t>
+          <t>2026-05-29 09:42:00.086</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779422020915</v>
+        <v>1780022518873</v>
       </c>
       <c r="C85" t="n">
-        <v>86707</v>
+        <v>83270</v>
       </c>
       <c r="D85" t="n">
-        <v>67.68000000000001</v>
+        <v>137.79</v>
       </c>
       <c r="E85" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="F85" t="n">
-        <v>805</v>
+        <v>420</v>
       </c>
       <c r="G85" t="n">
-        <v>65.76000000000001</v>
+        <v>367</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1211</v>
+      </c>
+      <c r="L85" t="n">
+        <v>125</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.325</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:38.996</t>
+          <t>2026-05-29 09:42:00.087</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779422021117</v>
+        <v>1780022519073</v>
       </c>
       <c r="C86" t="n">
-        <v>86948</v>
+        <v>82813</v>
       </c>
       <c r="D86" t="n">
-        <v>305.3</v>
+        <v>-326.1</v>
       </c>
       <c r="E86" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F86" t="n">
-        <v>867</v>
+        <v>420</v>
       </c>
       <c r="G86" t="n">
-        <v>62.44</v>
+        <v>367</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L86" t="n">
+        <v>109</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.307</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:39.608</t>
+          <t>2026-05-29 09:42:01.398</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779422021318</v>
+        <v>1780022519273</v>
       </c>
       <c r="C87" t="n">
-        <v>86180</v>
+        <v>83436</v>
       </c>
       <c r="D87" t="n">
-        <v>-477.97</v>
+        <v>313.21</v>
       </c>
       <c r="E87" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F87" t="n">
-        <v>867</v>
+        <v>420</v>
       </c>
       <c r="G87" t="n">
-        <v>62.44</v>
+        <v>367</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K87" t="n">
+        <v>2124</v>
+      </c>
+      <c r="L87" t="n">
+        <v>117</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.194</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:39.609</t>
+          <t>2026-05-29 09:42:01.399</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779422021519</v>
+        <v>1780022519473</v>
       </c>
       <c r="C88" t="n">
-        <v>86355</v>
+        <v>84035</v>
       </c>
       <c r="D88" t="n">
-        <v>-279.07</v>
+        <v>896.55</v>
       </c>
       <c r="E88" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F88" t="n">
-        <v>867</v>
+        <v>3298</v>
       </c>
       <c r="G88" t="n">
-        <v>62.44</v>
+        <v>367</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1925</v>
+      </c>
+      <c r="L88" t="n">
+        <v>109</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.034</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:39.609</t>
+          <t>2026-05-29 09:42:01.401</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779422021721</v>
+        <v>1780022519692</v>
       </c>
       <c r="C89" t="n">
-        <v>86543</v>
+        <v>84426</v>
       </c>
       <c r="D89" t="n">
-        <v>-77.12</v>
+        <v>1242.72</v>
       </c>
       <c r="E89" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F89" t="n">
-        <v>867</v>
+        <v>3298</v>
       </c>
       <c r="G89" t="n">
-        <v>62.44</v>
+        <v>367</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1708</v>
+      </c>
+      <c r="L89" t="n">
+        <v>123</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.067</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:40.020</t>
+          <t>2026-05-29 09:42:01.402</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779422021922</v>
+        <v>1780022519892</v>
       </c>
       <c r="C90" t="n">
-        <v>86785</v>
+        <v>83836</v>
       </c>
       <c r="D90" t="n">
-        <v>168.74</v>
+        <v>590.58</v>
       </c>
       <c r="E90" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F90" t="n">
-        <v>926</v>
+        <v>3298</v>
       </c>
       <c r="G90" t="n">
-        <v>68.92</v>
+        <v>367</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1509</v>
+      </c>
+      <c r="L90" t="n">
+        <v>108</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.922</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:40.020</t>
+          <t>2026-05-29 09:42:01.403</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779422022124</v>
+        <v>1780022520092</v>
       </c>
       <c r="C91" t="n">
-        <v>86182</v>
+        <v>84188</v>
       </c>
       <c r="D91" t="n">
-        <v>-442.7</v>
+        <v>913.05</v>
       </c>
       <c r="E91" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F91" t="n">
-        <v>926</v>
+        <v>3298</v>
       </c>
       <c r="G91" t="n">
-        <v>68.92</v>
+        <v>367</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1310</v>
+      </c>
+      <c r="L91" t="n">
+        <v>108</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.823</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:40.477</t>
+          <t>2026-05-29 09:42:01.404</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779422022325</v>
+        <v>1780022520292</v>
       </c>
       <c r="C92" t="n">
-        <v>86350</v>
+        <v>83931</v>
       </c>
       <c r="D92" t="n">
-        <v>-252.56</v>
+        <v>610.4</v>
       </c>
       <c r="E92" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F92" t="n">
-        <v>926</v>
+        <v>3298</v>
       </c>
       <c r="G92" t="n">
-        <v>68.92</v>
+        <v>367</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L92" t="n">
+        <v>114</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:40.478</t>
+          <t>2026-05-29 09:42:01.894</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779422022526</v>
+        <v>1780022520492</v>
       </c>
       <c r="C93" t="n">
-        <v>86594</v>
+        <v>82362</v>
       </c>
       <c r="D93" t="n">
-        <v>4.06</v>
+        <v>-989.12</v>
       </c>
       <c r="E93" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F93" t="n">
-        <v>926</v>
+        <v>3298</v>
       </c>
       <c r="G93" t="n">
-        <v>68.92</v>
+        <v>367</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1401</v>
+      </c>
+      <c r="L93" t="n">
+        <v>109</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.586</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:40.838</t>
+          <t>2026-05-29 09:42:01.895</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779422022728</v>
+        <v>1780022520692</v>
       </c>
       <c r="C94" t="n">
-        <v>86897</v>
+        <v>83911</v>
       </c>
       <c r="D94" t="n">
-        <v>306.86</v>
+        <v>609.34</v>
       </c>
       <c r="E94" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F94" t="n">
-        <v>765</v>
+        <v>3298</v>
       </c>
       <c r="G94" t="n">
-        <v>72.78</v>
+        <v>367</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J94" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1202</v>
+      </c>
+      <c r="L94" t="n">
+        <v>114</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.739</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:40.839</t>
+          <t>2026-05-29 09:42:01.895</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779422022929</v>
+        <v>1780022520892</v>
       </c>
       <c r="C95" t="n">
-        <v>86136</v>
+        <v>83303</v>
       </c>
       <c r="D95" t="n">
-        <v>-469.48</v>
+        <v>-29.13</v>
       </c>
       <c r="E95" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F95" t="n">
-        <v>765</v>
+        <v>3298</v>
       </c>
       <c r="G95" t="n">
-        <v>72.78</v>
+        <v>367</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J95" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1003</v>
+      </c>
+      <c r="L95" t="n">
+        <v>111</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.484</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:41.270</t>
+          <t>2026-05-29 09:42:02.139</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779422023131</v>
+        <v>1780022521111</v>
       </c>
       <c r="C96" t="n">
-        <v>86453</v>
+        <v>82874</v>
       </c>
       <c r="D96" t="n">
-        <v>-129.01</v>
+        <v>-456.67</v>
       </c>
       <c r="E96" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F96" t="n">
-        <v>765</v>
+        <v>3298</v>
       </c>
       <c r="G96" t="n">
-        <v>72.78</v>
+        <v>367</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1027</v>
+      </c>
+      <c r="L96" t="n">
+        <v>115</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:41.271</t>
+          <t>2026-05-29 09:42:02.141</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779422023332</v>
+        <v>1780022521311</v>
       </c>
       <c r="C97" t="n">
-        <v>86796</v>
+        <v>83239</v>
       </c>
       <c r="D97" t="n">
-        <v>220.44</v>
+        <v>-68.84</v>
       </c>
       <c r="E97" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="F97" t="n">
-        <v>765</v>
+        <v>3298</v>
       </c>
       <c r="G97" t="n">
-        <v>72.78</v>
+        <v>367</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>829</v>
+      </c>
+      <c r="L97" t="n">
+        <v>113</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:41.271</t>
+          <t>2026-05-29 09:42:03.223</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779422023533</v>
+        <v>1780022521511</v>
       </c>
       <c r="C98" t="n">
-        <v>87066</v>
+        <v>83881</v>
       </c>
       <c r="D98" t="n">
-        <v>479.42</v>
+        <v>576.6</v>
       </c>
       <c r="E98" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F98" t="n">
-        <v>745</v>
+        <v>2178</v>
       </c>
       <c r="G98" t="n">
-        <v>76.43000000000001</v>
+        <v>367</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1711</v>
+      </c>
+      <c r="L98" t="n">
+        <v>116</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.021</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:41.768</t>
+          <t>2026-05-29 09:42:03.225</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779422023735</v>
+        <v>1780022521711</v>
       </c>
       <c r="C99" t="n">
-        <v>86157</v>
+        <v>83573</v>
       </c>
       <c r="D99" t="n">
-        <v>-453.55</v>
+        <v>239.77</v>
       </c>
       <c r="E99" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F99" t="n">
-        <v>745</v>
+        <v>2178</v>
       </c>
       <c r="G99" t="n">
-        <v>76.43000000000001</v>
+        <v>367</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1513</v>
+      </c>
+      <c r="L99" t="n">
+        <v>118</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:41.768</t>
+          <t>2026-05-29 09:42:03.648</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779422023936</v>
+        <v>1780022521911</v>
       </c>
       <c r="C100" t="n">
-        <v>86401</v>
+        <v>83598</v>
       </c>
       <c r="D100" t="n">
-        <v>-186.87</v>
+        <v>252.78</v>
       </c>
       <c r="E100" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F100" t="n">
-        <v>745</v>
+        <v>2178</v>
       </c>
       <c r="G100" t="n">
-        <v>76.43000000000001</v>
+        <v>367</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L100" t="n">
+        <v>122</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:42.082</t>
+          <t>2026-05-29 09:42:03.669</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779422024138</v>
+        <v>1780022522111</v>
       </c>
       <c r="C101" t="n">
-        <v>86666</v>
+        <v>83591</v>
       </c>
       <c r="D101" t="n">
-        <v>87.47</v>
+        <v>233.14</v>
       </c>
       <c r="E101" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="F101" t="n">
-        <v>745</v>
+        <v>600</v>
       </c>
       <c r="G101" t="n">
-        <v>76.43000000000001</v>
+        <v>353.81</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1558</v>
+      </c>
+      <c r="L101" t="n">
+        <v>106</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.536</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:42.082</t>
+          <t>2026-05-29 09:42:03.671</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779422024339</v>
+        <v>1780022522311</v>
       </c>
       <c r="C102" t="n">
-        <v>86944</v>
+        <v>83054</v>
       </c>
       <c r="D102" t="n">
-        <v>361.1</v>
+        <v>-315.51</v>
       </c>
       <c r="E102" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="F102" t="n">
-        <v>846</v>
+        <v>600</v>
       </c>
       <c r="G102" t="n">
-        <v>75.33</v>
+        <v>353.81</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1359</v>
+      </c>
+      <c r="L102" t="n">
+        <v>111</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.695</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:42.501</t>
+          <t>2026-05-29 09:42:03.672</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779422024541</v>
+        <v>1780022522530</v>
       </c>
       <c r="C103" t="n">
-        <v>86072</v>
+        <v>82998</v>
       </c>
       <c r="D103" t="n">
-        <v>-528.96</v>
+        <v>-355.74</v>
       </c>
       <c r="E103" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="F103" t="n">
-        <v>846</v>
+        <v>600</v>
       </c>
       <c r="G103" t="n">
-        <v>75.33</v>
+        <v>353.81</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1141</v>
+      </c>
+      <c r="L103" t="n">
+        <v>109</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.584</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:42.502</t>
+          <t>2026-05-29 09:42:04.313</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779422024742</v>
+        <v>1780022522730</v>
       </c>
       <c r="C104" t="n">
-        <v>86347</v>
+        <v>83185</v>
       </c>
       <c r="D104" t="n">
-        <v>-227.51</v>
+        <v>-150.95</v>
       </c>
       <c r="E104" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="F104" t="n">
-        <v>846</v>
+        <v>600</v>
       </c>
       <c r="G104" t="n">
-        <v>75.33</v>
+        <v>353.81</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1582</v>
+      </c>
+      <c r="L104" t="n">
+        <v>110</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.829</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:42.809</t>
+          <t>2026-05-29 09:42:04.315</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779422024943</v>
+        <v>1780022522930</v>
       </c>
       <c r="C105" t="n">
-        <v>86666</v>
+        <v>82767</v>
       </c>
       <c r="D105" t="n">
-        <v>102.87</v>
+        <v>-561.4</v>
       </c>
       <c r="E105" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="F105" t="n">
-        <v>846</v>
+        <v>600</v>
       </c>
       <c r="G105" t="n">
-        <v>75.33</v>
+        <v>353.81</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J105" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1384</v>
+      </c>
+      <c r="L105" t="n">
+        <v>111</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.114</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:43.111</t>
+          <t>2026-05-29 09:42:04.316</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779422025145</v>
+        <v>1780022523130</v>
       </c>
       <c r="C106" t="n">
-        <v>86814</v>
+        <v>82516</v>
       </c>
       <c r="D106" t="n">
-        <v>245.72</v>
+        <v>-784.33</v>
       </c>
       <c r="E106" t="n">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="F106" t="n">
-        <v>766</v>
+        <v>600</v>
       </c>
       <c r="G106" t="n">
-        <v>73.45999999999999</v>
+        <v>353.81</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J106" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1185</v>
+      </c>
+      <c r="L106" t="n">
+        <v>112</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.668</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:43.112</t>
+          <t>2026-05-29 09:42:04.983</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779422025346</v>
+        <v>1780022523330</v>
       </c>
       <c r="C107" t="n">
-        <v>86183</v>
+        <v>82681</v>
       </c>
       <c r="D107" t="n">
-        <v>-397.56</v>
+        <v>-580.12</v>
       </c>
       <c r="E107" t="n">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="F107" t="n">
-        <v>766</v>
+        <v>600</v>
       </c>
       <c r="G107" t="n">
-        <v>73.45999999999999</v>
+        <v>353.81</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1652</v>
+      </c>
+      <c r="L107" t="n">
+        <v>124</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.982</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:43.533</t>
+          <t>2026-05-29 09:42:05.011</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779422025548</v>
+        <v>1780022523530</v>
       </c>
       <c r="C108" t="n">
-        <v>86509</v>
+        <v>82812</v>
       </c>
       <c r="D108" t="n">
-        <v>-51.69</v>
+        <v>-420.11</v>
       </c>
       <c r="E108" t="n">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="F108" t="n">
-        <v>766</v>
+        <v>600</v>
       </c>
       <c r="G108" t="n">
-        <v>73.45999999999999</v>
+        <v>353.81</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1480</v>
+      </c>
+      <c r="L108" t="n">
+        <v>110</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.801</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:43.548</t>
+          <t>2026-05-29 09:42:05.014</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779422025749</v>
+        <v>1780022523730</v>
       </c>
       <c r="C109" t="n">
-        <v>86844</v>
+        <v>82915</v>
       </c>
       <c r="D109" t="n">
-        <v>285.9</v>
+        <v>-296.11</v>
       </c>
       <c r="E109" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F109" t="n">
-        <v>685</v>
+        <v>1559</v>
       </c>
       <c r="G109" t="n">
-        <v>82.17</v>
+        <v>353.81</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1282</v>
+      </c>
+      <c r="L109" t="n">
+        <v>117</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.605</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:43.940</t>
+          <t>2026-05-29 09:42:05.387</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779422025950</v>
+        <v>1780022523930</v>
       </c>
       <c r="C110" t="n">
-        <v>86347</v>
+        <v>82677</v>
       </c>
       <c r="D110" t="n">
-        <v>-225.4</v>
+        <v>-519.3</v>
       </c>
       <c r="E110" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F110" t="n">
-        <v>685</v>
+        <v>1559</v>
       </c>
       <c r="G110" t="n">
-        <v>82.17</v>
+        <v>353.81</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1455</v>
+      </c>
+      <c r="L110" t="n">
+        <v>144</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.847</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:43.947</t>
+          <t>2026-05-29 09:42:05.390</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779422026152</v>
+        <v>1780022524149</v>
       </c>
       <c r="C111" t="n">
-        <v>86516</v>
+        <v>82303</v>
       </c>
       <c r="D111" t="n">
-        <v>-45.13</v>
+        <v>-867.33</v>
       </c>
       <c r="E111" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F111" t="n">
-        <v>685</v>
+        <v>1559</v>
       </c>
       <c r="G111" t="n">
-        <v>82.17</v>
+        <v>353.81</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L111" t="n">
+        <v>114</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.465</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:44.341</t>
+          <t>2026-05-29 09:42:05.392</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779422026353</v>
+        <v>1780022524349</v>
       </c>
       <c r="C112" t="n">
-        <v>87028</v>
+        <v>83217</v>
       </c>
       <c r="D112" t="n">
-        <v>469.13</v>
+        <v>90.03</v>
       </c>
       <c r="E112" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F112" t="n">
-        <v>685</v>
+        <v>1559</v>
       </c>
       <c r="G112" t="n">
-        <v>82.17</v>
+        <v>353.81</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1041</v>
+      </c>
+      <c r="L112" t="n">
+        <v>116</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.286</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:44.341</t>
+          <t>2026-05-29 09:42:05.622</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779422026555</v>
+        <v>1780022524549</v>
       </c>
       <c r="C113" t="n">
-        <v>87388</v>
+        <v>83018</v>
       </c>
       <c r="D113" t="n">
-        <v>805.67</v>
+        <v>-113.47</v>
       </c>
       <c r="E113" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F113" t="n">
-        <v>725</v>
+        <v>779</v>
       </c>
       <c r="G113" t="n">
-        <v>71.69</v>
+        <v>325.98</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1071</v>
+      </c>
+      <c r="L113" t="n">
+        <v>123</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.508</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:44.815</t>
+          <t>2026-05-29 09:42:05.623</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779422026756</v>
+        <v>1780022524749</v>
       </c>
       <c r="C114" t="n">
-        <v>86516</v>
+        <v>82729</v>
       </c>
       <c r="D114" t="n">
-        <v>-106.61</v>
+        <v>-396.8</v>
       </c>
       <c r="E114" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F114" t="n">
-        <v>725</v>
+        <v>779</v>
       </c>
       <c r="G114" t="n">
-        <v>71.69</v>
+        <v>325.98</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>873</v>
+      </c>
+      <c r="L114" t="n">
+        <v>105</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.128</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:44.816</t>
+          <t>2026-05-29 09:42:06.034</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779422026957</v>
+        <v>1780022524949</v>
       </c>
       <c r="C115" t="n">
-        <v>86369</v>
+        <v>82484</v>
       </c>
       <c r="D115" t="n">
-        <v>-248.28</v>
+        <v>-621.96</v>
       </c>
       <c r="E115" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F115" t="n">
-        <v>725</v>
+        <v>779</v>
       </c>
       <c r="G115" t="n">
-        <v>71.69</v>
+        <v>325.98</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1083</v>
+      </c>
+      <c r="L115" t="n">
+        <v>117</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.834</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:45.200</t>
+          <t>2026-05-29 09:42:06.036</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779422027159</v>
+        <v>1780022525149</v>
       </c>
       <c r="C116" t="n">
-        <v>86494</v>
+        <v>82331</v>
       </c>
       <c r="D116" t="n">
-        <v>-110.87</v>
+        <v>-743.86</v>
       </c>
       <c r="E116" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F116" t="n">
-        <v>725</v>
+        <v>779</v>
       </c>
       <c r="G116" t="n">
-        <v>71.69</v>
+        <v>325.98</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K116" t="n">
+        <v>886</v>
+      </c>
+      <c r="L116" t="n">
+        <v>115</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.063</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:45.200</t>
+          <t>2026-05-29 09:42:06.703</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779422027360</v>
+        <v>1780022525349</v>
       </c>
       <c r="C117" t="n">
-        <v>86661</v>
+        <v>82190</v>
       </c>
       <c r="D117" t="n">
-        <v>61.68</v>
+        <v>-847.67</v>
       </c>
       <c r="E117" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F117" t="n">
-        <v>725</v>
+        <v>779</v>
       </c>
       <c r="G117" t="n">
-        <v>71.69</v>
+        <v>325.98</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1353</v>
+      </c>
+      <c r="L117" t="n">
+        <v>116</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.961</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:45.555</t>
+          <t>2026-05-29 09:42:06.743</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779422027562</v>
+        <v>1780022525549</v>
       </c>
       <c r="C118" t="n">
-        <v>86632</v>
+        <v>83477</v>
       </c>
       <c r="D118" t="n">
-        <v>29.59</v>
+        <v>481.72</v>
       </c>
       <c r="E118" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F118" t="n">
-        <v>725</v>
+        <v>779</v>
       </c>
       <c r="G118" t="n">
-        <v>71.69</v>
+        <v>325.98</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1192</v>
+      </c>
+      <c r="L118" t="n">
+        <v>117</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.497</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:45.556</t>
+          <t>2026-05-29 09:42:07.091</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779422027763</v>
+        <v>1780022525768</v>
       </c>
       <c r="C119" t="n">
-        <v>85189</v>
+        <v>83354</v>
       </c>
       <c r="D119" t="n">
-        <v>-1414.89</v>
+        <v>334.63</v>
       </c>
       <c r="E119" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F119" t="n">
-        <v>725</v>
+        <v>1179</v>
       </c>
       <c r="G119" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1322</v>
+      </c>
+      <c r="L119" t="n">
+        <v>124</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.277</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:45.991</t>
+          <t>2026-05-29 09:42:07.126</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779422027964</v>
+        <v>1780022525968</v>
       </c>
       <c r="C120" t="n">
-        <v>84827</v>
+        <v>82808</v>
       </c>
       <c r="D120" t="n">
-        <v>-1706.14</v>
+        <v>-228.1</v>
       </c>
       <c r="E120" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F120" t="n">
-        <v>725</v>
+        <v>1179</v>
       </c>
       <c r="G120" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L120" t="n">
+        <v>117</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.719</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:45.992</t>
+          <t>2026-05-29 09:42:07.127</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779422028166</v>
+        <v>1780022526168</v>
       </c>
       <c r="C121" t="n">
-        <v>84954</v>
+        <v>82605</v>
       </c>
       <c r="D121" t="n">
-        <v>-1493.83</v>
+        <v>-419.69</v>
       </c>
       <c r="E121" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F121" t="n">
-        <v>725</v>
+        <v>1179</v>
       </c>
       <c r="G121" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>959</v>
+      </c>
+      <c r="L121" t="n">
+        <v>106</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.658</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:46.369</t>
+          <t>2026-05-29 09:42:07.883</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779422028367</v>
+        <v>1780022526368</v>
       </c>
       <c r="C122" t="n">
-        <v>85587</v>
+        <v>83776</v>
       </c>
       <c r="D122" t="n">
-        <v>-786.14</v>
+        <v>772.29</v>
       </c>
       <c r="E122" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F122" t="n">
-        <v>725</v>
+        <v>1179</v>
       </c>
       <c r="G122" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1513</v>
+      </c>
+      <c r="L122" t="n">
+        <v>117</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1.424</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:46.370</t>
+          <t>2026-05-29 09:42:07.903</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779422028569</v>
+        <v>1780022526568</v>
       </c>
       <c r="C123" t="n">
-        <v>84838</v>
+        <v>83138</v>
       </c>
       <c r="D123" t="n">
-        <v>-1495.84</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="E123" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F123" t="n">
-        <v>725</v>
+        <v>1179</v>
       </c>
       <c r="G123" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1334</v>
+      </c>
+      <c r="L123" t="n">
+        <v>119</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.055</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:46.875</t>
+          <t>2026-05-29 09:42:07.904</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779422028770</v>
+        <v>1780022526768</v>
       </c>
       <c r="C124" t="n">
-        <v>85115</v>
+        <v>82753</v>
       </c>
       <c r="D124" t="n">
-        <v>-1144.04</v>
+        <v>-294.11</v>
       </c>
       <c r="E124" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F124" t="n">
-        <v>725</v>
+        <v>1179</v>
       </c>
       <c r="G124" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L124" t="n">
+        <v>112</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.988</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:46.876</t>
+          <t>2026-05-29 09:42:08.615</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779422028972</v>
+        <v>1780022526968</v>
       </c>
       <c r="C125" t="n">
-        <v>85145</v>
+        <v>83097</v>
       </c>
       <c r="D125" t="n">
-        <v>-1056.84</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E125" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F125" t="n">
-        <v>725</v>
+        <v>1179</v>
       </c>
       <c r="G125" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1646</v>
+      </c>
+      <c r="L125" t="n">
+        <v>107</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.092</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:47.216</t>
+          <t>2026-05-29 09:42:08.646</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779422029173</v>
+        <v>1780022527187</v>
       </c>
       <c r="C126" t="n">
-        <v>85566</v>
+        <v>83381</v>
       </c>
       <c r="D126" t="n">
-        <v>-583</v>
+        <v>345.37</v>
       </c>
       <c r="E126" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F126" t="n">
-        <v>2658</v>
+        <v>1559</v>
       </c>
       <c r="G126" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1456</v>
+      </c>
+      <c r="L126" t="n">
+        <v>118</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.988</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:47.217</t>
+          <t>2026-05-29 09:42:08.647</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779422029374</v>
+        <v>1780022527387</v>
       </c>
       <c r="C127" t="n">
-        <v>85057</v>
+        <v>83148</v>
       </c>
       <c r="D127" t="n">
-        <v>-1062.85</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F127" t="n">
-        <v>2658</v>
+        <v>1559</v>
       </c>
       <c r="G127" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1259</v>
+      </c>
+      <c r="L127" t="n">
+        <v>98</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.335</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:47.623</t>
+          <t>2026-05-29 09:42:09.017</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779422029576</v>
+        <v>1780022527587</v>
       </c>
       <c r="C128" t="n">
-        <v>85308</v>
+        <v>83276</v>
       </c>
       <c r="D128" t="n">
-        <v>-758.71</v>
+        <v>218.34</v>
       </c>
       <c r="E128" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F128" t="n">
-        <v>2658</v>
+        <v>1559</v>
       </c>
       <c r="G128" t="n">
-        <v>71.69</v>
+        <v>331.1</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1429</v>
+      </c>
+      <c r="L128" t="n">
+        <v>113</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.163</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:47.624</t>
+          <t>2026-05-29 09:42:09.022</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779422029777</v>
+        <v>1780022527787</v>
       </c>
       <c r="C129" t="n">
-        <v>85570</v>
+        <v>83265</v>
       </c>
       <c r="D129" t="n">
-        <v>-458.77</v>
+        <v>196.43</v>
       </c>
       <c r="E129" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F129" t="n">
-        <v>625</v>
+        <v>1559</v>
       </c>
       <c r="G129" t="n">
-        <v>89.06</v>
+        <v>331.1</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1234</v>
+      </c>
+      <c r="L129" t="n">
+        <v>113</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.868</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:48.013</t>
+          <t>2026-05-29 09:42:09.023</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779422029979</v>
+        <v>1780022527987</v>
       </c>
       <c r="C130" t="n">
-        <v>85773</v>
+        <v>83014</v>
       </c>
       <c r="D130" t="n">
-        <v>-232.83</v>
+        <v>-64.39</v>
       </c>
       <c r="E130" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F130" t="n">
-        <v>625</v>
+        <v>1559</v>
       </c>
       <c r="G130" t="n">
-        <v>89.06</v>
+        <v>331.1</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1036</v>
+      </c>
+      <c r="L130" t="n">
+        <v>106</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.681</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:48.014</t>
+          <t>2026-05-29 09:42:12.757</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779422030180</v>
+        <v>1780022528188</v>
       </c>
       <c r="C131" t="n">
-        <v>85002</v>
+        <v>82581</v>
       </c>
       <c r="D131" t="n">
-        <v>-992.1900000000001</v>
+        <v>-494.17</v>
       </c>
       <c r="E131" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F131" t="n">
-        <v>625</v>
+        <v>1559</v>
       </c>
       <c r="G131" t="n">
-        <v>89.06</v>
+        <v>331.1</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K131" t="n">
+        <v>4568</v>
+      </c>
+      <c r="L131" t="n">
+        <v>109</v>
+      </c>
+      <c r="M131" t="n">
+        <v>1.056</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:48.451</t>
+          <t>2026-05-29 09:42:12.758</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779422030381</v>
+        <v>1780022528387</v>
       </c>
       <c r="C132" t="n">
-        <v>85210</v>
+        <v>82889</v>
       </c>
       <c r="D132" t="n">
-        <v>-734.58</v>
+        <v>-161.47</v>
       </c>
       <c r="E132" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F132" t="n">
-        <v>625</v>
+        <v>1559</v>
       </c>
       <c r="G132" t="n">
-        <v>89.06</v>
+        <v>331.1</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>4371</v>
+      </c>
+      <c r="L132" t="n">
+        <v>115</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.834</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:48.451</t>
+          <t>2026-05-29 09:42:12.760</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779422030583</v>
+        <v>1780022528606</v>
       </c>
       <c r="C133" t="n">
-        <v>85426</v>
+        <v>82521</v>
       </c>
       <c r="D133" t="n">
-        <v>-481.85</v>
+        <v>-521.39</v>
       </c>
       <c r="E133" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F133" t="n">
-        <v>625</v>
+        <v>1559</v>
       </c>
       <c r="G133" t="n">
-        <v>89.06</v>
+        <v>331.1</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K133" t="n">
+        <v>4153</v>
+      </c>
+      <c r="L133" t="n">
+        <v>119</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.891</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:48.826</t>
+          <t>2026-05-29 09:42:12.761</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779422030784</v>
+        <v>1780022528806</v>
       </c>
       <c r="C134" t="n">
-        <v>85659</v>
+        <v>82484</v>
       </c>
       <c r="D134" t="n">
-        <v>-224.76</v>
+        <v>-532.3200000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F134" t="n">
-        <v>946</v>
+        <v>1559</v>
       </c>
       <c r="G134" t="n">
-        <v>104.13</v>
+        <v>331.1</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3954</v>
+      </c>
+      <c r="L134" t="n">
+        <v>122</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.208</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:48.826</t>
+          <t>2026-05-29 09:42:12.762</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779422030986</v>
+        <v>1780022529006</v>
       </c>
       <c r="C135" t="n">
-        <v>85097</v>
+        <v>82736</v>
       </c>
       <c r="D135" t="n">
-        <v>-775.52</v>
+        <v>-253.71</v>
       </c>
       <c r="E135" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F135" t="n">
-        <v>946</v>
+        <v>1559</v>
       </c>
       <c r="G135" t="n">
-        <v>104.13</v>
+        <v>331.1</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>3755</v>
+      </c>
+      <c r="L135" t="n">
+        <v>107</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.994</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:49.239</t>
+          <t>2026-05-29 09:42:12.763</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779422031187</v>
+        <v>1780022529206</v>
       </c>
       <c r="C136" t="n">
-        <v>85368</v>
+        <v>82548</v>
       </c>
       <c r="D136" t="n">
-        <v>-465.75</v>
+        <v>-429.02</v>
       </c>
       <c r="E136" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F136" t="n">
-        <v>946</v>
+        <v>1959</v>
       </c>
       <c r="G136" t="n">
-        <v>104.13</v>
+        <v>331.1</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3556</v>
+      </c>
+      <c r="L136" t="n">
+        <v>107</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.771</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:49.245</t>
+          <t>2026-05-29 09:42:13.215</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779422031388</v>
+        <v>1780022529406</v>
       </c>
       <c r="C137" t="n">
-        <v>85626</v>
+        <v>82732</v>
       </c>
       <c r="D137" t="n">
-        <v>-184.46</v>
+        <v>-223.57</v>
       </c>
       <c r="E137" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F137" t="n">
-        <v>725</v>
+        <v>1959</v>
       </c>
       <c r="G137" t="n">
-        <v>102.07</v>
+        <v>331.1</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>3808</v>
+      </c>
+      <c r="L137" t="n">
+        <v>108</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:49.660</t>
+          <t>2026-05-29 09:42:13.226</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779422031590</v>
+        <v>1780022529606</v>
       </c>
       <c r="C138" t="n">
-        <v>85763</v>
+        <v>83149</v>
       </c>
       <c r="D138" t="n">
-        <v>-38.24</v>
+        <v>204.61</v>
       </c>
       <c r="E138" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F138" t="n">
-        <v>725</v>
+        <v>400</v>
       </c>
       <c r="G138" t="n">
-        <v>102.07</v>
+        <v>299.19</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J138" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K138" t="n">
+        <v>3619</v>
+      </c>
+      <c r="L138" t="n">
+        <v>109</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.248</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:49.686</t>
+          <t>2026-05-29 09:42:13.253</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779422031791</v>
+        <v>1780022529806</v>
       </c>
       <c r="C139" t="n">
-        <v>85260</v>
+        <v>83049</v>
       </c>
       <c r="D139" t="n">
-        <v>-539.3200000000001</v>
+        <v>94.38</v>
       </c>
       <c r="E139" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F139" t="n">
-        <v>725</v>
+        <v>400</v>
       </c>
       <c r="G139" t="n">
-        <v>102.07</v>
+        <v>299.19</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J139" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3445</v>
+      </c>
+      <c r="L139" t="n">
+        <v>102</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1.211</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:49.939</t>
+          <t>2026-05-29 09:42:13.283</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779422031993</v>
+        <v>1780022530006</v>
       </c>
       <c r="C140" t="n">
-        <v>85478</v>
+        <v>83146</v>
       </c>
       <c r="D140" t="n">
-        <v>-294.36</v>
+        <v>186.66</v>
       </c>
       <c r="E140" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F140" t="n">
-        <v>725</v>
+        <v>400</v>
       </c>
       <c r="G140" t="n">
-        <v>102.07</v>
+        <v>299.19</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J140" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K140" t="n">
+        <v>3276</v>
+      </c>
+      <c r="L140" t="n">
+        <v>108</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.448</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 10:53:50.283</t>
+          <t>2026-05-29 09:42:14.259</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779422032194</v>
+        <v>1780022530653</v>
       </c>
       <c r="C141" t="n">
-        <v>85674</v>
+        <v>83418</v>
       </c>
       <c r="D141" t="n">
-        <v>-83.64</v>
+        <v>449.33</v>
       </c>
       <c r="E141" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="F141" t="n">
-        <v>786</v>
+        <v>400</v>
       </c>
       <c r="G141" t="n">
-        <v>87.70999999999999</v>
+        <v>299.19</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:50.304</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1779422032395</v>
-      </c>
-      <c r="C142" t="n">
-        <v>85718</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-35.46</v>
-      </c>
-      <c r="E142" t="n">
-        <v>79</v>
-      </c>
-      <c r="F142" t="n">
-        <v>786</v>
-      </c>
-      <c r="G142" t="n">
-        <v>87.70999999999999</v>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:50.688</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>1779422032597</v>
-      </c>
-      <c r="C143" t="n">
-        <v>85216</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-535.6900000000001</v>
-      </c>
-      <c r="E143" t="n">
-        <v>79</v>
-      </c>
-      <c r="F143" t="n">
-        <v>786</v>
-      </c>
-      <c r="G143" t="n">
-        <v>87.70999999999999</v>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:50.718</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>1779422032798</v>
-      </c>
-      <c r="C144" t="n">
-        <v>85507</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-217.9</v>
-      </c>
-      <c r="E144" t="n">
-        <v>79</v>
-      </c>
-      <c r="F144" t="n">
-        <v>786</v>
-      </c>
-      <c r="G144" t="n">
-        <v>87.70999999999999</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:51.293</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>1779422033000</v>
-      </c>
-      <c r="C145" t="n">
-        <v>85782</v>
-      </c>
-      <c r="D145" t="n">
-        <v>67.98999999999999</v>
-      </c>
-      <c r="E145" t="n">
-        <v>73</v>
-      </c>
-      <c r="F145" t="n">
-        <v>805</v>
-      </c>
-      <c r="G145" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:51.294</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779422033201</v>
-      </c>
-      <c r="C146" t="n">
-        <v>85915</v>
-      </c>
-      <c r="D146" t="n">
-        <v>197.59</v>
-      </c>
-      <c r="E146" t="n">
-        <v>73</v>
-      </c>
-      <c r="F146" t="n">
-        <v>805</v>
-      </c>
-      <c r="G146" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:51.299</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779422033402</v>
-      </c>
-      <c r="C147" t="n">
-        <v>85249</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-478.29</v>
-      </c>
-      <c r="E147" t="n">
-        <v>73</v>
-      </c>
-      <c r="F147" t="n">
-        <v>805</v>
-      </c>
-      <c r="G147" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:51.837</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779422033604</v>
-      </c>
-      <c r="C148" t="n">
-        <v>85373</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-330.37</v>
-      </c>
-      <c r="E148" t="n">
-        <v>73</v>
-      </c>
-      <c r="F148" t="n">
-        <v>805</v>
-      </c>
-      <c r="G148" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:51.838</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779422033805</v>
-      </c>
-      <c r="C149" t="n">
-        <v>85588</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-98.84999999999999</v>
-      </c>
-      <c r="E149" t="n">
-        <v>73</v>
-      </c>
-      <c r="F149" t="n">
-        <v>805</v>
-      </c>
-      <c r="G149" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:53:52.226</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779422034007</v>
-      </c>
-      <c r="C150" t="n">
-        <v>85473</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-208.91</v>
-      </c>
-      <c r="E150" t="n">
-        <v>73</v>
-      </c>
-      <c r="F150" t="n">
-        <v>947</v>
-      </c>
-      <c r="G150" t="n">
-        <v>105.12</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I141" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J141" t="n">
+        <v>35.49</v>
+      </c>
+      <c r="K141" t="n">
+        <v>3605</v>
+      </c>
+      <c r="L141" t="n">
+        <v>108</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.187</v>
       </c>
     </row>
   </sheetData>
